--- a/artfynd/A 30254-2026 artfynd.xlsx
+++ b/artfynd/A 30254-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866748</v>
       </c>
       <c r="B2" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135866640</v>
       </c>
       <c r="B3" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135866736</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135866584</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135866594</v>
       </c>
       <c r="B8" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135866612</v>
       </c>
       <c r="B9" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>135866620</v>
       </c>
       <c r="B10" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>135866634</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135866658</v>
       </c>
       <c r="B12" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135866661</v>
       </c>
       <c r="B13" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135866667</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135866697</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>135866714</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135866725</v>
       </c>
       <c r="B17" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>135866732</v>
       </c>
       <c r="B18" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135866737</v>
       </c>
       <c r="B19" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>135866752</v>
       </c>
       <c r="B20" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135866755</v>
       </c>
       <c r="B21" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135866758</v>
       </c>
       <c r="B22" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>135866762</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135866564</v>
       </c>
       <c r="B24" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135866570</v>
       </c>
       <c r="B25" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 30254-2026 artfynd.xlsx
+++ b/artfynd/A 30254-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866748</v>
       </c>
       <c r="B2" t="n">
-        <v>92446</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135866640</v>
       </c>
       <c r="B3" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135866736</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135866629</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>135866809</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135866584</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135866594</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135866612</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>135866620</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>135866634</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135866658</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135866661</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135866667</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135866697</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>135866714</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135866725</v>
       </c>
       <c r="B17" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>135866732</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135866737</v>
       </c>
       <c r="B19" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>135866752</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135866755</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135866758</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>135866762</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135866564</v>
       </c>
       <c r="B24" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135866570</v>
       </c>
       <c r="B25" t="n">
-        <v>101485</v>
+        <v>101502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 30254-2026 artfynd.xlsx
+++ b/artfynd/A 30254-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866748</v>
       </c>
       <c r="B2" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135866640</v>
       </c>
       <c r="B3" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135866736</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135866584</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135866594</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135866612</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>135866620</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>135866634</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135866658</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135866661</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135866667</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135866697</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>135866714</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135866725</v>
       </c>
       <c r="B17" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>135866732</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135866737</v>
       </c>
       <c r="B19" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>135866752</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135866755</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135866758</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>135866762</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135866564</v>
       </c>
       <c r="B24" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135866570</v>
       </c>
       <c r="B25" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 30254-2026 artfynd.xlsx
+++ b/artfynd/A 30254-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866748</v>
       </c>
       <c r="B2" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135866640</v>
       </c>
       <c r="B3" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135866736</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135866584</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135866594</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135866612</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>135866620</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>135866634</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135866658</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135866661</v>
       </c>
       <c r="B13" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135866667</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135866697</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>135866714</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135866725</v>
       </c>
       <c r="B17" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>135866732</v>
       </c>
       <c r="B18" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135866737</v>
       </c>
       <c r="B19" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>135866752</v>
       </c>
       <c r="B20" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135866755</v>
       </c>
       <c r="B21" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135866758</v>
       </c>
       <c r="B22" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>135866762</v>
       </c>
       <c r="B23" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135866564</v>
       </c>
       <c r="B24" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135866570</v>
       </c>
       <c r="B25" t="n">
-        <v>101504</v>
+        <v>101505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 30254-2026 artfynd.xlsx
+++ b/artfynd/A 30254-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866748</v>
       </c>
       <c r="B2" t="n">
-        <v>92462</v>
+        <v>92463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135866640</v>
       </c>
       <c r="B3" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135866736</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135866629</v>
       </c>
       <c r="B5" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>135866809</v>
       </c>
       <c r="B6" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135866584</v>
       </c>
       <c r="B7" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135866594</v>
       </c>
       <c r="B8" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135866612</v>
       </c>
       <c r="B9" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>135866620</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>135866634</v>
       </c>
       <c r="B11" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135866658</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135866661</v>
       </c>
       <c r="B13" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135866667</v>
       </c>
       <c r="B14" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135866697</v>
       </c>
       <c r="B15" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>135866714</v>
       </c>
       <c r="B16" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135866725</v>
       </c>
       <c r="B17" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>135866732</v>
       </c>
       <c r="B18" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135866737</v>
       </c>
       <c r="B19" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>135866752</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135866755</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135866758</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>135866762</v>
       </c>
       <c r="B23" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135866564</v>
       </c>
       <c r="B24" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135866570</v>
       </c>
       <c r="B25" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 30254-2026 artfynd.xlsx
+++ b/artfynd/A 30254-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866748</v>
       </c>
       <c r="B2" t="n">
-        <v>92463</v>
+        <v>92469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135866640</v>
       </c>
       <c r="B3" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135866736</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135866629</v>
       </c>
       <c r="B5" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>135866809</v>
       </c>
       <c r="B6" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135866584</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135866594</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135866612</v>
       </c>
       <c r="B9" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>135866620</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>135866634</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135866658</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135866661</v>
       </c>
       <c r="B13" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135866667</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135866697</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>135866714</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135866725</v>
       </c>
       <c r="B17" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>135866732</v>
       </c>
       <c r="B18" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135866737</v>
       </c>
       <c r="B19" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>135866752</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135866755</v>
       </c>
       <c r="B21" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135866758</v>
       </c>
       <c r="B22" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>135866762</v>
       </c>
       <c r="B23" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135866564</v>
       </c>
       <c r="B24" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135866570</v>
       </c>
       <c r="B25" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 30254-2026 artfynd.xlsx
+++ b/artfynd/A 30254-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135866748</v>
       </c>
       <c r="B2" t="n">
-        <v>92469</v>
+        <v>92470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135866640</v>
       </c>
       <c r="B3" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135866736</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>135866629</v>
       </c>
       <c r="B5" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>135866809</v>
       </c>
       <c r="B6" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>135866584</v>
       </c>
       <c r="B7" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>135866594</v>
       </c>
       <c r="B8" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135866612</v>
       </c>
       <c r="B9" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>135866620</v>
       </c>
       <c r="B10" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>135866634</v>
       </c>
       <c r="B11" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135866658</v>
       </c>
       <c r="B12" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135866661</v>
       </c>
       <c r="B13" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>135866667</v>
       </c>
       <c r="B14" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>135866697</v>
       </c>
       <c r="B15" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>135866714</v>
       </c>
       <c r="B16" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135866725</v>
       </c>
       <c r="B17" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>135866732</v>
       </c>
       <c r="B18" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>135866737</v>
       </c>
       <c r="B19" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>135866752</v>
       </c>
       <c r="B20" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>135866755</v>
       </c>
       <c r="B21" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>135866758</v>
       </c>
       <c r="B22" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         <v>135866762</v>
       </c>
       <c r="B23" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135866564</v>
       </c>
       <c r="B24" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>135866570</v>
       </c>
       <c r="B25" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
